--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755604147_individual_h_2.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755604147_individual_h_2.xlsx
@@ -658,7 +658,7 @@
         <v>0.008407015632763826</v>
       </c>
       <c r="C2" t="n">
-        <v>12692760</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12692760</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>9867439</v>
+        <v>4820422</v>
       </c>
       <c r="L2" t="n">
-        <v>6252445</v>
+        <v>2990667</v>
       </c>
       <c r="M2" t="n">
-        <v>1694175</v>
+        <v>782685</v>
       </c>
       <c r="N2" t="n">
-        <v>116954</v>
+        <v>45306</v>
       </c>
       <c r="O2" t="n">
-        <v>967750</v>
+        <v>459126</v>
       </c>
       <c r="P2" t="n">
-        <v>372123</v>
+        <v>179467</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999946355819702</v>
+        <v>0.9999938607215881</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9772182703018188</v>
+        <v>0.9560461640357971</v>
       </c>
       <c r="S2" t="n">
-        <v>0.938062846660614</v>
+        <v>0.8915311098098755</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9230307936668396</v>
+        <v>0.8631466627120972</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8597915172576904</v>
+        <v>0.70884770154953</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9490862488746643</v>
+        <v>0.9004818797111511</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9658432602882385</v>
+        <v>0.9325383305549622</v>
       </c>
       <c r="X2" t="n">
-        <v>12692760</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,43 +742,43 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>12692760</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>9714356</v>
+        <v>4854570</v>
       </c>
       <c r="AG2" t="n">
-        <v>5956664</v>
+        <v>2980268</v>
       </c>
       <c r="AH2" t="n">
-        <v>1601221</v>
+        <v>800821</v>
       </c>
       <c r="AI2" t="n">
-        <v>118175</v>
+        <v>59096</v>
       </c>
       <c r="AJ2" t="n">
-        <v>917973</v>
+        <v>459081</v>
       </c>
       <c r="AK2" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9567423462867737</v>
+        <v>0.9567334651947021</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.911146342754364</v>
+        <v>0.9111363887786865</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582749962806702</v>
+        <v>0.8581864833831787</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6627725958824158</v>
+        <v>0.6625929474830627</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020447134971619</v>
+        <v>0.9019822478294373</v>
       </c>
       <c r="AR2" t="n">
         <v>0.931419849395752</v>
@@ -795,13 +795,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9867439</v>
+        <v>4820422</v>
       </c>
       <c r="E3" t="n">
-        <v>271547</v>
+        <v>244494</v>
       </c>
       <c r="F3" t="n">
-        <v>3729</v>
+        <v>3690</v>
       </c>
       <c r="G3" t="n">
         <v>594</v>
@@ -813,109 +813,109 @@
         <v>17</v>
       </c>
       <c r="J3" t="n">
-        <v>20139172</v>
+        <v>10069581</v>
       </c>
       <c r="K3" t="n">
-        <v>22458546</v>
+        <v>11125076</v>
       </c>
       <c r="L3" t="n">
-        <v>25873374</v>
+        <v>12777275</v>
       </c>
       <c r="M3" t="n">
-        <v>30823862</v>
+        <v>15358194</v>
       </c>
       <c r="N3" t="n">
-        <v>32634474</v>
+        <v>16308126</v>
       </c>
       <c r="O3" t="n">
-        <v>31761923</v>
+        <v>15856066</v>
       </c>
       <c r="P3" t="n">
-        <v>32432295</v>
+        <v>16209735</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9727925062179565</v>
+        <v>0.9509035348892212</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9551845192909241</v>
+        <v>0.9132189750671387</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9074973464012146</v>
+        <v>0.8382527828216553</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6553733944892883</v>
+        <v>0.5075449347496033</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9504872560501099</v>
+        <v>0.9016738533973694</v>
       </c>
       <c r="W3" t="n">
-        <v>0.962689995765686</v>
+        <v>0.9285241365432739</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>9714356</v>
+        <v>4854570</v>
       </c>
       <c r="Z3" t="n">
-        <v>398208</v>
+        <v>199283</v>
       </c>
       <c r="AA3" t="n">
-        <v>17110</v>
+        <v>8572</v>
       </c>
       <c r="AB3" t="n">
-        <v>13592</v>
+        <v>6807</v>
       </c>
       <c r="AC3" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>20139240</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>22249364</v>
+        <v>11127154</v>
       </c>
       <c r="AG3" t="n">
-        <v>25705317</v>
+        <v>12850470</v>
       </c>
       <c r="AH3" t="n">
-        <v>30700729</v>
+        <v>15349956</v>
       </c>
       <c r="AI3" t="n">
-        <v>32593417</v>
+        <v>16296642</v>
       </c>
       <c r="AJ3" t="n">
-        <v>31714153</v>
+        <v>15856919</v>
       </c>
       <c r="AK3" t="n">
-        <v>32418947</v>
+        <v>16209464</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9577006697654724</v>
+        <v>0.957639753818512</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099981188774109</v>
+        <v>0.9100435376167297</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.85770583152771</v>
+        <v>0.8576763868331909</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6622154712677002</v>
+        <v>0.6620287895202637</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015981554985046</v>
+        <v>0.9015854597091675</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313740730285645</v>
+        <v>0.931328296661377</v>
       </c>
     </row>
     <row r="4">
@@ -929,13 +929,13 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>215225</v>
+        <v>207001</v>
       </c>
       <c r="E4" t="n">
-        <v>6252445</v>
+        <v>2990667</v>
       </c>
       <c r="F4" t="n">
-        <v>75673</v>
+        <v>74740</v>
       </c>
       <c r="G4" t="n">
         <v>1237</v>
@@ -947,109 +947,109 @@
         <v>53</v>
       </c>
       <c r="J4" t="n">
+        <v>39</v>
+      </c>
+      <c r="K4" t="n">
+        <v>221617</v>
+      </c>
+      <c r="L4" t="n">
+        <v>363862</v>
+      </c>
+      <c r="M4" t="n">
+        <v>124096</v>
+      </c>
+      <c r="N4" t="n">
+        <v>18609</v>
+      </c>
+      <c r="O4" t="n">
+        <v>50741</v>
+      </c>
+      <c r="P4" t="n">
+        <v>12983</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.9999969601631165</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.9534679055213928</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.9022447466850281</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.8505176305770874</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.5915393233299255</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.9010774493217468</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.9305269122123718</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>204986</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2980268</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>82895</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>5498</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1148</v>
+      </c>
+      <c r="AD4" t="n">
         <v>68</v>
       </c>
-      <c r="K4" t="n">
-        <v>230038</v>
-      </c>
-      <c r="L4" t="n">
-        <v>412828</v>
-      </c>
-      <c r="M4" t="n">
-        <v>141273</v>
-      </c>
-      <c r="N4" t="n">
-        <v>19072</v>
-      </c>
-      <c r="O4" t="n">
-        <v>51915</v>
-      </c>
-      <c r="P4" t="n">
-        <v>13160</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.9999973177909851</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.9750003814697266</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.9465462565422058</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.9151981472969055</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.7437929511070251</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.9497861862182617</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.9642640352249146</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>410116</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>5956664</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>165604</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>10994</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2284</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>136</v>
-      </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>439220</v>
+        <v>219539</v>
       </c>
       <c r="AG4" t="n">
-        <v>580885</v>
+        <v>290667</v>
       </c>
       <c r="AH4" t="n">
-        <v>264406</v>
+        <v>132334</v>
       </c>
       <c r="AI4" t="n">
-        <v>60129</v>
+        <v>30093</v>
       </c>
       <c r="AJ4" t="n">
-        <v>99685</v>
+        <v>49888</v>
       </c>
       <c r="AK4" t="n">
-        <v>26508</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9572212696075439</v>
+        <v>0.9571864008903503</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9105718731880188</v>
+        <v>0.9105896949768066</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8579903244972229</v>
+        <v>0.8579313158988953</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.662493884563446</v>
+        <v>0.662310779094696</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018213748931885</v>
+        <v>0.90178382396698</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313969612121582</v>
+        <v>0.9313740730285645</v>
       </c>
     </row>
     <row r="5">
@@ -1059,127 +1059,127 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>8569</v>
+        <v>8418</v>
       </c>
       <c r="E5" t="n">
-        <v>125198</v>
+        <v>103961</v>
       </c>
       <c r="F5" t="n">
-        <v>1694175</v>
+        <v>782685</v>
       </c>
       <c r="G5" t="n">
-        <v>9137</v>
+        <v>8867</v>
       </c>
       <c r="H5" t="n">
-        <v>29183</v>
+        <v>29177</v>
       </c>
       <c r="I5" t="n">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>275977</v>
+        <v>248885</v>
       </c>
       <c r="L5" t="n">
-        <v>293353</v>
+        <v>284196</v>
       </c>
       <c r="M5" t="n">
-        <v>172690</v>
+        <v>151025</v>
       </c>
       <c r="N5" t="n">
-        <v>61500</v>
+        <v>43959</v>
       </c>
       <c r="O5" t="n">
-        <v>50412</v>
+        <v>50067</v>
       </c>
       <c r="P5" t="n">
-        <v>14422</v>
+        <v>13815</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999979138374329</v>
+        <v>0.999997615814209</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9845877289772034</v>
+        <v>0.9713388085365295</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9784910678863525</v>
+        <v>0.9605227708816528</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9904372692108154</v>
+        <v>0.9832406640052795</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9975459575653076</v>
+        <v>0.9961885809898376</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9968833327293396</v>
+        <v>0.9938591718673706</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9991599321365356</v>
+        <v>0.9983675479888916</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>16069</v>
+        <v>8031</v>
       </c>
       <c r="Z5" t="n">
-        <v>170194</v>
+        <v>85136</v>
       </c>
       <c r="AA5" t="n">
-        <v>1601221</v>
+        <v>800821</v>
       </c>
       <c r="AB5" t="n">
-        <v>19877</v>
+        <v>9950</v>
       </c>
       <c r="AC5" t="n">
-        <v>58238</v>
+        <v>29139</v>
       </c>
       <c r="AD5" t="n">
-        <v>1266</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>429060</v>
+        <v>214737</v>
       </c>
       <c r="AG5" t="n">
-        <v>589134</v>
+        <v>294595</v>
       </c>
       <c r="AH5" t="n">
-        <v>265644</v>
+        <v>132889</v>
       </c>
       <c r="AI5" t="n">
-        <v>60279</v>
+        <v>30169</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100189</v>
+        <v>50112</v>
       </c>
       <c r="AK5" t="n">
-        <v>26527</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735538363456726</v>
+        <v>0.9735455513000488</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643634557723999</v>
+        <v>0.9643480777740479</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.983855664730072</v>
+        <v>0.9838436245918274</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.996332585811615</v>
+        <v>0.9963290691375732</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939122200012207</v>
+        <v>0.9939084053039551</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983846545219421</v>
+        <v>0.9983840584754944</v>
       </c>
     </row>
     <row r="6">
@@ -1189,22 +1189,22 @@
         <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>6203</v>
+        <v>6157</v>
       </c>
       <c r="E6" t="n">
-        <v>15194</v>
+        <v>14519</v>
       </c>
       <c r="F6" t="n">
-        <v>31854</v>
+        <v>15654</v>
       </c>
       <c r="G6" t="n">
-        <v>116954</v>
+        <v>45306</v>
       </c>
       <c r="H6" t="n">
-        <v>7803</v>
+        <v>7197</v>
       </c>
       <c r="I6" t="n">
-        <v>435</v>
+        <v>421</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>12924</v>
+        <v>6466</v>
       </c>
       <c r="Z6" t="n">
-        <v>10697</v>
+        <v>5355</v>
       </c>
       <c r="AA6" t="n">
-        <v>21742</v>
+        <v>10880</v>
       </c>
       <c r="AB6" t="n">
-        <v>118175</v>
+        <v>59096</v>
       </c>
       <c r="AC6" t="n">
-        <v>13954</v>
+        <v>6987</v>
       </c>
       <c r="AD6" t="n">
-        <v>962</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1266,19 +1266,19 @@
         <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="F7" t="n">
-        <v>29684</v>
+        <v>29680</v>
       </c>
       <c r="G7" t="n">
-        <v>7853</v>
+        <v>7675</v>
       </c>
       <c r="H7" t="n">
-        <v>967750</v>
+        <v>459126</v>
       </c>
       <c r="I7" t="n">
-        <v>12052</v>
+        <v>11890</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>1624</v>
+        <v>812</v>
       </c>
       <c r="AA7" t="n">
-        <v>59290</v>
+        <v>29657</v>
       </c>
       <c r="AB7" t="n">
-        <v>15136</v>
+        <v>7573</v>
       </c>
       <c r="AC7" t="n">
-        <v>917973</v>
+        <v>459081</v>
       </c>
       <c r="AD7" t="n">
-        <v>24084</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,7 +1334,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
         <v>17</v>
@@ -1343,16 +1343,16 @@
         <v>92</v>
       </c>
       <c r="F8" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G8" t="n">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H8" t="n">
-        <v>13675</v>
+        <v>13113</v>
       </c>
       <c r="I8" t="n">
-        <v>372123</v>
+        <v>179467</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>660</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>530</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>25119</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
